--- a/templates/成绩导入模板.xlsx
+++ b/templates/成绩导入模板.xlsx
@@ -452,7 +452,7 @@
         <v>作文</v>
       </c>
       <c r="L1" t="str">
-        <v>口语</v>
+        <v>听说</v>
       </c>
       <c r="M1" t="str">
         <v>总分</v>
@@ -472,34 +472,34 @@
         <v>示例学生一</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2">
         <v>9</v>
       </c>
       <c r="F2">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <v>13</v>
       </c>
       <c r="L2">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="M2">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="N2">
         <v>1</v>
@@ -516,31 +516,31 @@
         <v>示例学生二</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3">
         <v>8</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="G3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="J3">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K3">
         <v>12</v>
       </c>
       <c r="L3">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="M3" t="str">
         <v/>
@@ -558,7 +558,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A8"/>
   <cols>
     <col min="1" max="1" width="95.83203125" customWidth="1"/>
   </cols>
@@ -570,7 +570,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>1. 表头固定为：班级、学号、姓名、语法选择、完形填空、阅读理解、回答问题、选词填空、完成句子、短文填空、作文、口语、总分、排名</v>
+        <v>1. 表头固定为：班级、学号、姓名、语法选择、完形填空、阅读理解、回答问题、选词填空、完成句子、短文填空、作文、听说、总分、排名</v>
       </c>
     </row>
     <row r="3">
@@ -580,22 +580,32 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>3. 导入时会按「学号」自动匹配班级学生档案，未匹配的学生也会保留但标记</v>
+        <v>3. 各题型满分（默认 120 分制）：语法选择 10 分，完形填空 10 分，阅读理解 30 分，回答问题 10 分，选词填空 5 分，完成句子 5 分，短文填空 5 分，作文 15 分，听说 30 分</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>4. 一个文件可以包含多个班的成绩（按「班级」列自动分发），也可以每班一个文件</v>
+        <v>4. 导入时会按「学号」自动匹配班级学生档案，未匹配的学生也会保留但标记</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>5. 也可以不导入，直接在平台的「查看/编辑」页面手工录入</v>
+        <v>5. 一个文件可以包含多个班的成绩（按「班级」列自动分发），也可以每班一个文件</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>6. 「班级」列支持 1班 / 801 / 801班 等写法；「听说」列旧模板写「口语」也能识别</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>7. 也可以不导入，直接在平台的「查看/编辑」页面手工录入</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A8"/>
   </ignoredErrors>
 </worksheet>
 </file>